--- a/tests/fixtures/ctpe_shape/batch1/has_finding/b1_has.xlsx
+++ b/tests/fixtures/ctpe_shape/batch1/has_finding/b1_has.xlsx
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44688.46527777778</v>
+        <v>47882.17013888889</v>
       </c>
       <c r="H3" t="n">
         <v>28.4</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44688.46527777778</v>
+        <v>47882.17013888889</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
